--- a/Structure_Data/text.9.14/20260914_152/structure_factor_20260914_152.xlsx
+++ b/Structure_Data/text.9.14/20260914_152/structure_factor_20260914_152.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D374"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,3872 @@
         <v>19.6241552895842</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.321544647216797</v>
+      </c>
+      <c r="C30">
+        <v>0.320381164550781</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.321544647216797</v>
+      </c>
+      <c r="C31">
+        <v>0.320381164550781</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.281547546386719</v>
+      </c>
+      <c r="C32">
+        <v>0.275012969970703</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.225185394287109</v>
+      </c>
+      <c r="C33">
+        <v>0.186351776123047</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.202583312988281</v>
+      </c>
+      <c r="C34">
+        <v>0.0554084777832031</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.191608428955078</v>
+      </c>
+      <c r="C35">
+        <v>0.0447769165039062</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.138191223144531</v>
+      </c>
+      <c r="C36">
+        <v>0.0270843505859375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.112804412841797</v>
+      </c>
+      <c r="C37">
+        <v>0.0248565673828125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.0949058532714844</v>
+      </c>
+      <c r="C38">
+        <v>0.0245780944824219</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.0623245239257812</v>
+      </c>
+      <c r="C39">
+        <v>0.00111770629882812</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0508537292480469</v>
+      </c>
+      <c r="C40">
+        <v>0.000392913818359375</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.0412063598632812</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0409164428710938</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.0347671508789062</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>0.0264854431152344</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B45">
+        <v>0.0245018005371094</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B46">
+        <v>0.0197563171386719</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B47">
+        <v>0.0188179016113281</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B48">
+        <v>0.0187759399414062</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B49">
+        <v>0.0194015502929688</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B50">
+        <v>0.0169029235839844</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B51">
+        <v>0.0159912109375</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>2.5</v>
+      </c>
+      <c r="B52">
+        <v>0.0157661437988281</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B53">
+        <v>0.0141868591308594</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B54">
+        <v>0.0126457214355469</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B55">
+        <v>0.01318359375</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B56">
+        <v>0.0119590759277344</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B57">
+        <v>0.0118179321289062</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B58">
+        <v>0.0117530822753906</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B59">
+        <v>0.0077362060546875</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B60">
+        <v>0.00757217407226562</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61">
+        <v>0.00732040405273438</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B62">
+        <v>0.00741958618164062</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B63">
+        <v>0.00705718994140625</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B64">
+        <v>0.00673675537109375</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B65">
+        <v>0.00589370727539062</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>3.5</v>
+      </c>
+      <c r="B66">
+        <v>0</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>18252</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>2.30908941485865</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>2.35842294356641</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.05</v>
+      </c>
+      <c r="B82">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.1</v>
+      </c>
+      <c r="B83">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.15</v>
+      </c>
+      <c r="B84">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.2</v>
+      </c>
+      <c r="B85">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.25</v>
+      </c>
+      <c r="B86">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.3</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.35</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.4</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.45</v>
+      </c>
+      <c r="B90">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.5</v>
+      </c>
+      <c r="B91">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.55</v>
+      </c>
+      <c r="B92">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.6</v>
+      </c>
+      <c r="B93">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.65</v>
+      </c>
+      <c r="B94">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.7</v>
+      </c>
+      <c r="B95">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.75</v>
+      </c>
+      <c r="B96">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.8</v>
+      </c>
+      <c r="B97">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.85</v>
+      </c>
+      <c r="B98">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.9</v>
+      </c>
+      <c r="B99">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.95</v>
+      </c>
+      <c r="B100">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>0.5</v>
+      </c>
+      <c r="B102">
+        <v>5118</v>
+      </c>
+      <c r="C102">
+        <v>0.280407626561473</v>
+      </c>
+      <c r="D102">
+        <v>0.280407626561473</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>1</v>
+      </c>
+      <c r="B103">
+        <v>3032</v>
+      </c>
+      <c r="C103">
+        <v>0.166118781503397</v>
+      </c>
+      <c r="D103">
+        <v>0.44652640806487</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>1.5</v>
+      </c>
+      <c r="B104">
+        <v>2153</v>
+      </c>
+      <c r="C104">
+        <v>0.117959675651983</v>
+      </c>
+      <c r="D104">
+        <v>0.564486083716853</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>2</v>
+      </c>
+      <c r="B105">
+        <v>1608</v>
+      </c>
+      <c r="C105">
+        <v>0.0880999342537804</v>
+      </c>
+      <c r="D105">
+        <v>0.652586017970633</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>2.5</v>
+      </c>
+      <c r="B106">
+        <v>1248</v>
+      </c>
+      <c r="C106">
+        <v>0.0683760683760684</v>
+      </c>
+      <c r="D106">
+        <v>0.720962086346702</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>3</v>
+      </c>
+      <c r="B107">
+        <v>985</v>
+      </c>
+      <c r="C107">
+        <v>0.0539666885820732</v>
+      </c>
+      <c r="D107">
+        <v>0.774928774928775</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>3.5</v>
+      </c>
+      <c r="B108">
+        <v>754</v>
+      </c>
+      <c r="C108">
+        <v>0.0413105413105413</v>
+      </c>
+      <c r="D108">
+        <v>0.816239316239316</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>4</v>
+      </c>
+      <c r="B109">
+        <v>600</v>
+      </c>
+      <c r="C109">
+        <v>0.0328731097961867</v>
+      </c>
+      <c r="D109">
+        <v>0.849112426035503</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>4.5</v>
+      </c>
+      <c r="B110">
+        <v>438</v>
+      </c>
+      <c r="C110">
+        <v>0.0239973701512163</v>
+      </c>
+      <c r="D110">
+        <v>0.873109796186719</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>5</v>
+      </c>
+      <c r="B111">
+        <v>369</v>
+      </c>
+      <c r="C111">
+        <v>0.0202169625246548</v>
+      </c>
+      <c r="D111">
+        <v>0.893326758711374</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>5.5</v>
+      </c>
+      <c r="B112">
+        <v>347</v>
+      </c>
+      <c r="C112">
+        <v>0.0190116151654613</v>
+      </c>
+      <c r="D112">
+        <v>0.912338373876835</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>6</v>
+      </c>
+      <c r="B113">
+        <v>244</v>
+      </c>
+      <c r="C113">
+        <v>0.0133683979837826</v>
+      </c>
+      <c r="D113">
+        <v>0.925706771860618</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>6.5</v>
+      </c>
+      <c r="B114">
+        <v>240</v>
+      </c>
+      <c r="C114">
+        <v>0.0131492439184747</v>
+      </c>
+      <c r="D114">
+        <v>0.938856015779093</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>7</v>
+      </c>
+      <c r="B115">
+        <v>211</v>
+      </c>
+      <c r="C115">
+        <v>0.0115603769449923</v>
+      </c>
+      <c r="D115">
+        <v>0.950416392724085</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>7.5</v>
+      </c>
+      <c r="B116">
+        <v>178</v>
+      </c>
+      <c r="C116">
+        <v>0.00975235590620206</v>
+      </c>
+      <c r="D116">
+        <v>0.960168748630287</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>8</v>
+      </c>
+      <c r="B117">
+        <v>136</v>
+      </c>
+      <c r="C117">
+        <v>0.00745123822046899</v>
+      </c>
+      <c r="D117">
+        <v>0.967619986850756</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>8.5</v>
+      </c>
+      <c r="B118">
+        <v>80</v>
+      </c>
+      <c r="C118">
+        <v>0.00438308130615823</v>
+      </c>
+      <c r="D118">
+        <v>0.972003068156914</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>9</v>
+      </c>
+      <c r="B119">
+        <v>94</v>
+      </c>
+      <c r="C119">
+        <v>0.00515012053473592</v>
+      </c>
+      <c r="D119">
+        <v>0.97715318869165</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>9.5</v>
+      </c>
+      <c r="B120">
+        <v>81</v>
+      </c>
+      <c r="C120">
+        <v>0.00443786982248521</v>
+      </c>
+      <c r="D120">
+        <v>0.981591058514135</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>10</v>
+      </c>
+      <c r="B121">
+        <v>57</v>
+      </c>
+      <c r="C121">
+        <v>0.00312294543063774</v>
+      </c>
+      <c r="D121">
+        <v>0.984714003944773</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>10.5</v>
+      </c>
+      <c r="B122">
+        <v>63</v>
+      </c>
+      <c r="C122">
+        <v>0.00345167652859961</v>
+      </c>
+      <c r="D122">
+        <v>0.988165680473373</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>11</v>
+      </c>
+      <c r="B123">
+        <v>36</v>
+      </c>
+      <c r="C123">
+        <v>0.0019723865877712</v>
+      </c>
+      <c r="D123">
+        <v>0.990138067061144</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>11.5</v>
+      </c>
+      <c r="B124">
+        <v>37</v>
+      </c>
+      <c r="C124">
+        <v>0.00202717510409818</v>
+      </c>
+      <c r="D124">
+        <v>0.992165242165242</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>12</v>
+      </c>
+      <c r="B125">
+        <v>29</v>
+      </c>
+      <c r="C125">
+        <v>0.00158886697348236</v>
+      </c>
+      <c r="D125">
+        <v>0.993754109138725</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>12.5</v>
+      </c>
+      <c r="B126">
+        <v>24</v>
+      </c>
+      <c r="C126">
+        <v>0.00131492439184747</v>
+      </c>
+      <c r="D126">
+        <v>0.995069033530572</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>13</v>
+      </c>
+      <c r="B127">
+        <v>17</v>
+      </c>
+      <c r="C127">
+        <v>0.000931404777558624</v>
+      </c>
+      <c r="D127">
+        <v>0.996000438308131</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>13.5</v>
+      </c>
+      <c r="B128">
+        <v>17</v>
+      </c>
+      <c r="C128">
+        <v>0.000931404777558624</v>
+      </c>
+      <c r="D128">
+        <v>0.996931843085689</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>14</v>
+      </c>
+      <c r="B129">
+        <v>11</v>
+      </c>
+      <c r="C129">
+        <v>0.000602673679596757</v>
+      </c>
+      <c r="D129">
+        <v>0.997534516765286</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>14.5</v>
+      </c>
+      <c r="B130">
+        <v>8</v>
+      </c>
+      <c r="C130">
+        <v>0.000438308130615823</v>
+      </c>
+      <c r="D130">
+        <v>0.997972824895902</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>15</v>
+      </c>
+      <c r="B131">
+        <v>7</v>
+      </c>
+      <c r="C131">
+        <v>0.000383519614288845</v>
+      </c>
+      <c r="D131">
+        <v>0.998356344510191</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>15.5</v>
+      </c>
+      <c r="B132">
+        <v>5</v>
+      </c>
+      <c r="C132">
+        <v>0.000273942581634889</v>
+      </c>
+      <c r="D132">
+        <v>0.998630287091826</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>16</v>
+      </c>
+      <c r="B133">
+        <v>6</v>
+      </c>
+      <c r="C133">
+        <v>0.000328731097961867</v>
+      </c>
+      <c r="D133">
+        <v>0.998959018189787</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>16.5</v>
+      </c>
+      <c r="B134">
+        <v>1</v>
+      </c>
+      <c r="C134">
+        <v>5.47885163269779e-05</v>
+      </c>
+      <c r="D134">
+        <v>0.999013806706114</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>17</v>
+      </c>
+      <c r="B135">
+        <v>5</v>
+      </c>
+      <c r="C135">
+        <v>0.000273942581634889</v>
+      </c>
+      <c r="D135">
+        <v>0.999287749287749</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>17.5</v>
+      </c>
+      <c r="B136">
+        <v>4</v>
+      </c>
+      <c r="C136">
+        <v>0.000219154065307911</v>
+      </c>
+      <c r="D136">
+        <v>0.999506903353057</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>18.5</v>
+      </c>
+      <c r="B137">
+        <v>1</v>
+      </c>
+      <c r="C137">
+        <v>5.47885163269779e-05</v>
+      </c>
+      <c r="D137">
+        <v>0.999561691869384</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>19</v>
+      </c>
+      <c r="B138">
+        <v>2</v>
+      </c>
+      <c r="C138">
+        <v>0.000109577032653956</v>
+      </c>
+      <c r="D138">
+        <v>0.999671268902038</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>19.5</v>
+      </c>
+      <c r="B139">
+        <v>2</v>
+      </c>
+      <c r="C139">
+        <v>0.000109577032653956</v>
+      </c>
+      <c r="D139">
+        <v>0.999780845934692</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>20.5</v>
+      </c>
+      <c r="B140">
+        <v>1</v>
+      </c>
+      <c r="C140">
+        <v>5.47885163269779e-05</v>
+      </c>
+      <c r="D140">
+        <v>0.999835634451019</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>21</v>
+      </c>
+      <c r="B141">
+        <v>2</v>
+      </c>
+      <c r="C141">
+        <v>0.000109577032653956</v>
+      </c>
+      <c r="D141">
+        <v>0.999945211483673</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>21.5</v>
+      </c>
+      <c r="B142">
+        <v>1</v>
+      </c>
+      <c r="C142">
+        <v>5.47885163269779e-05</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143"/>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>177853</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.888237485319259</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>0.397388059410438</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>0.05</v>
+      </c>
+      <c r="B157">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>0.1</v>
+      </c>
+      <c r="B158">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>0.15</v>
+      </c>
+      <c r="B159">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>0.2</v>
+      </c>
+      <c r="B160">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>0.25</v>
+      </c>
+      <c r="B161">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>0.3</v>
+      </c>
+      <c r="B162">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>0.35</v>
+      </c>
+      <c r="B163">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>0.4</v>
+      </c>
+      <c r="B164">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>0.45</v>
+      </c>
+      <c r="B165">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>0.5</v>
+      </c>
+      <c r="B166">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>0.55</v>
+      </c>
+      <c r="B167">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>0.6</v>
+      </c>
+      <c r="B168">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>0.65</v>
+      </c>
+      <c r="B169">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>0.7</v>
+      </c>
+      <c r="B170">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>0.75</v>
+      </c>
+      <c r="B171">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>0.8</v>
+      </c>
+      <c r="B172">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>0.85</v>
+      </c>
+      <c r="B173">
+        <v>1.4142135623731</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>0.9</v>
+      </c>
+      <c r="B174">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>0.95</v>
+      </c>
+      <c r="B175">
+        <v>1.6583123951777</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>0.5</v>
+      </c>
+      <c r="B177">
+        <v>60013</v>
+      </c>
+      <c r="C177">
+        <v>0.337430349783248</v>
+      </c>
+      <c r="D177">
+        <v>0.337430349783248</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B178">
+        <v>33391</v>
+      </c>
+      <c r="C178">
+        <v>0.187744935424199</v>
+      </c>
+      <c r="D178">
+        <v>0.525175285207447</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B179">
+        <v>13981</v>
+      </c>
+      <c r="C179">
+        <v>0.0786098632016328</v>
+      </c>
+      <c r="D179">
+        <v>0.603785148409079</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>1</v>
+      </c>
+      <c r="B180">
+        <v>11103</v>
+      </c>
+      <c r="C180">
+        <v>0.0624279601693533</v>
+      </c>
+      <c r="D180">
+        <v>0.666213108578433</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B181">
+        <v>20914</v>
+      </c>
+      <c r="C181">
+        <v>0.117591494099059</v>
+      </c>
+      <c r="D181">
+        <v>0.783804602677492</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B182">
+        <v>9867</v>
+      </c>
+      <c r="C182">
+        <v>0.0554784007017031</v>
+      </c>
+      <c r="D182">
+        <v>0.839283003379195</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B183">
+        <v>7710</v>
+      </c>
+      <c r="C183">
+        <v>0.0433504073588863</v>
+      </c>
+      <c r="D183">
+        <v>0.882633410738081</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>1.5</v>
+      </c>
+      <c r="B184">
+        <v>8122</v>
+      </c>
+      <c r="C184">
+        <v>0.0456669271814364</v>
+      </c>
+      <c r="D184">
+        <v>0.928300337919518</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B185">
+        <v>3281</v>
+      </c>
+      <c r="C185">
+        <v>0.0184478192664729</v>
+      </c>
+      <c r="D185">
+        <v>0.946748157185991</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B186">
+        <v>2539</v>
+      </c>
+      <c r="C186">
+        <v>0.0142758345375113</v>
+      </c>
+      <c r="D186">
+        <v>0.961023991723502</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B187">
+        <v>1014</v>
+      </c>
+      <c r="C187">
+        <v>0.00570133762151889</v>
+      </c>
+      <c r="D187">
+        <v>0.966725329345021</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B188">
+        <v>2177</v>
+      </c>
+      <c r="C188">
+        <v>0.0122404457613872</v>
+      </c>
+      <c r="D188">
+        <v>0.978965775106408</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B189">
+        <v>1568</v>
+      </c>
+      <c r="C189">
+        <v>0.00881626961591876</v>
+      </c>
+      <c r="D189">
+        <v>0.987782044722327</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2</v>
+      </c>
+      <c r="B190">
+        <v>452</v>
+      </c>
+      <c r="C190">
+        <v>0.00254142465969087</v>
+      </c>
+      <c r="D190">
+        <v>0.990323469382018</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B191">
+        <v>974</v>
+      </c>
+      <c r="C191">
+        <v>0.00547643278437811</v>
+      </c>
+      <c r="D191">
+        <v>0.995799902166396</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B192">
+        <v>272</v>
+      </c>
+      <c r="C192">
+        <v>0.00152935289255734</v>
+      </c>
+      <c r="D192">
+        <v>0.997329255058953</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B193">
+        <v>153</v>
+      </c>
+      <c r="C193">
+        <v>0.000860261002063502</v>
+      </c>
+      <c r="D193">
+        <v>0.998189516061017</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B194">
+        <v>104</v>
+      </c>
+      <c r="C194">
+        <v>0.00058475257656604</v>
+      </c>
+      <c r="D194">
+        <v>0.998774268637583</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B195">
+        <v>76</v>
+      </c>
+      <c r="C195">
+        <v>0.000427319190567491</v>
+      </c>
+      <c r="D195">
+        <v>0.99920158782815</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B196">
+        <v>30</v>
+      </c>
+      <c r="C196">
+        <v>0.000168678627855589</v>
+      </c>
+      <c r="D196">
+        <v>0.999370266456006</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B197">
+        <v>48</v>
+      </c>
+      <c r="C197">
+        <v>0.000269885804568942</v>
+      </c>
+      <c r="D197">
+        <v>0.999640152260575</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>2.5</v>
+      </c>
+      <c r="B198">
+        <v>30</v>
+      </c>
+      <c r="C198">
+        <v>0.000168678627855589</v>
+      </c>
+      <c r="D198">
+        <v>0.99980883088843</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B199">
+        <v>20</v>
+      </c>
+      <c r="C199">
+        <v>0.000112452418570392</v>
+      </c>
+      <c r="D199">
+        <v>0.999921283307001</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B200">
+        <v>3</v>
+      </c>
+      <c r="C200">
+        <v>1.68678627855589e-05</v>
+      </c>
+      <c r="D200">
+        <v>0.999938151169786</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B201">
+        <v>5</v>
+      </c>
+      <c r="C201">
+        <v>2.81131046425981e-05</v>
+      </c>
+      <c r="D201">
+        <v>0.999966264274429</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B202">
+        <v>4</v>
+      </c>
+      <c r="C202">
+        <v>2.24904837140785e-05</v>
+      </c>
+      <c r="D202">
+        <v>0.999988754758143</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>5.62262092851962e-06</v>
+      </c>
+      <c r="D203">
+        <v>0.999994377379071</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B204">
+        <v>1</v>
+      </c>
+      <c r="C204">
+        <v>5.62262092851962e-06</v>
+      </c>
+      <c r="D204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205"/>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B210">
+        <v>0.321544647216797</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B211">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>0</v>
+      </c>
+      <c r="B216">
+        <v>0.321544647216797</v>
+      </c>
+      <c r="C216">
+        <v>1</v>
+      </c>
+      <c r="D216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>0.5</v>
+      </c>
+      <c r="B217">
+        <v>0.252082824707031</v>
+      </c>
+      <c r="C217">
+        <v>6</v>
+      </c>
+      <c r="D217">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>1</v>
+      </c>
+      <c r="B218">
+        <v>0.221622467041016</v>
+      </c>
+      <c r="C218">
+        <v>26</v>
+      </c>
+      <c r="D218">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>1.5</v>
+      </c>
+      <c r="B219">
+        <v>0.185335371229384</v>
+      </c>
+      <c r="C219">
+        <v>90</v>
+      </c>
+      <c r="D219">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>2</v>
+      </c>
+      <c r="B220">
+        <v>0.159397523794601</v>
+      </c>
+      <c r="C220">
+        <v>134</v>
+      </c>
+      <c r="D220">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>2.5</v>
+      </c>
+      <c r="B221">
+        <v>0.138687370359436</v>
+      </c>
+      <c r="C221">
+        <v>258</v>
+      </c>
+      <c r="D221">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>3</v>
+      </c>
+      <c r="B222">
+        <v>0.123383256865711</v>
+      </c>
+      <c r="C222">
+        <v>410</v>
+      </c>
+      <c r="D222">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>3.5</v>
+      </c>
+      <c r="B223">
+        <v>0.114259048029479</v>
+      </c>
+      <c r="C223">
+        <v>494</v>
+      </c>
+      <c r="D223">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>4</v>
+      </c>
+      <c r="B224">
+        <v>0.109728108281675</v>
+      </c>
+      <c r="C224">
+        <v>690</v>
+      </c>
+      <c r="D224">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>4.5</v>
+      </c>
+      <c r="B225">
+        <v>0.107931719996082</v>
+      </c>
+      <c r="C225">
+        <v>962</v>
+      </c>
+      <c r="D225">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>5</v>
+      </c>
+      <c r="B226">
+        <v>0.107564429333518</v>
+      </c>
+      <c r="C226">
+        <v>1098</v>
+      </c>
+      <c r="D226">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>5.5</v>
+      </c>
+      <c r="B227">
+        <v>0.10739251322631</v>
+      </c>
+      <c r="C227">
+        <v>1406</v>
+      </c>
+      <c r="D227">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>6</v>
+      </c>
+      <c r="B228">
+        <v>0.106778583599134</v>
+      </c>
+      <c r="C228">
+        <v>1578</v>
+      </c>
+      <c r="D228">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>6.5</v>
+      </c>
+      <c r="B229">
+        <v>0.10588617769058</v>
+      </c>
+      <c r="C229">
+        <v>2018</v>
+      </c>
+      <c r="D229">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>7</v>
+      </c>
+      <c r="B230">
+        <v>0.104898066728366</v>
+      </c>
+      <c r="C230">
+        <v>2342</v>
+      </c>
+      <c r="D230">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>7.5</v>
+      </c>
+      <c r="B231">
+        <v>0.104098749414211</v>
+      </c>
+      <c r="C231">
+        <v>2634</v>
+      </c>
+      <c r="D231">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>8</v>
+      </c>
+      <c r="B232">
+        <v>0.103433802998513</v>
+      </c>
+      <c r="C232">
+        <v>2930</v>
+      </c>
+      <c r="D232">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>8.5</v>
+      </c>
+      <c r="B233">
+        <v>0.102927872323065</v>
+      </c>
+      <c r="C233">
+        <v>3402</v>
+      </c>
+      <c r="D233">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>9</v>
+      </c>
+      <c r="B234">
+        <v>0.102634062648002</v>
+      </c>
+      <c r="C234">
+        <v>3926</v>
+      </c>
+      <c r="D234">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>9.5</v>
+      </c>
+      <c r="B235">
+        <v>0.102512563498882</v>
+      </c>
+      <c r="C235">
+        <v>4266</v>
+      </c>
+      <c r="D235">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>10</v>
+      </c>
+      <c r="B236">
+        <v>0.102573530265695</v>
+      </c>
+      <c r="C236">
+        <v>4730</v>
+      </c>
+      <c r="D236">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>10.5</v>
+      </c>
+      <c r="B237">
+        <v>0.102657060571245</v>
+      </c>
+      <c r="C237">
+        <v>5510</v>
+      </c>
+      <c r="D237">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>11</v>
+      </c>
+      <c r="B238">
+        <v>0.102818097797327</v>
+      </c>
+      <c r="C238">
+        <v>5562</v>
+      </c>
+      <c r="D238">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>11.5</v>
+      </c>
+      <c r="B239">
+        <v>0.102891584565971</v>
+      </c>
+      <c r="C239">
+        <v>6410</v>
+      </c>
+      <c r="D239">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>12</v>
+      </c>
+      <c r="B240">
+        <v>0.102916647808981</v>
+      </c>
+      <c r="C240">
+        <v>6894</v>
+      </c>
+      <c r="D240">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>12.5</v>
+      </c>
+      <c r="B241">
+        <v>0.102921596674798</v>
+      </c>
+      <c r="C241">
+        <v>7490</v>
+      </c>
+      <c r="D241">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>13</v>
+      </c>
+      <c r="B242">
+        <v>0.102818773398534</v>
+      </c>
+      <c r="C242">
+        <v>8258</v>
+      </c>
+      <c r="D242">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>13.5</v>
+      </c>
+      <c r="B243">
+        <v>0.102723714375936</v>
+      </c>
+      <c r="C243">
+        <v>8994</v>
+      </c>
+      <c r="D243">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>14</v>
+      </c>
+      <c r="B244">
+        <v>0.102674529887144</v>
+      </c>
+      <c r="C244">
+        <v>9446</v>
+      </c>
+      <c r="D244">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>14.5</v>
+      </c>
+      <c r="B245">
+        <v>0.102618220717904</v>
+      </c>
+      <c r="C245">
+        <v>9978</v>
+      </c>
+      <c r="D245">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>15</v>
+      </c>
+      <c r="B246">
+        <v>0.102662162349219</v>
+      </c>
+      <c r="C246">
+        <v>11138</v>
+      </c>
+      <c r="D246">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>15.5</v>
+      </c>
+      <c r="B247">
+        <v>0.102656001733642</v>
+      </c>
+      <c r="C247">
+        <v>11406</v>
+      </c>
+      <c r="D247">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>16</v>
+      </c>
+      <c r="B248">
+        <v>0.102725255522529</v>
+      </c>
+      <c r="C248">
+        <v>12575</v>
+      </c>
+      <c r="D248">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>16.5</v>
+      </c>
+      <c r="B249">
+        <v>0.102858486983132</v>
+      </c>
+      <c r="C249">
+        <v>12848</v>
+      </c>
+      <c r="D249">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>17</v>
+      </c>
+      <c r="B250">
+        <v>0.103101997944846</v>
+      </c>
+      <c r="C250">
+        <v>12060</v>
+      </c>
+      <c r="D250">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>17.5</v>
+      </c>
+      <c r="B251">
+        <v>0.103202349935213</v>
+      </c>
+      <c r="C251">
+        <v>11804</v>
+      </c>
+      <c r="D251">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>18</v>
+      </c>
+      <c r="B252">
+        <v>0.10334441241096</v>
+      </c>
+      <c r="C252">
+        <v>11016</v>
+      </c>
+      <c r="D252">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>18.5</v>
+      </c>
+      <c r="B253">
+        <v>0.103378360070915</v>
+      </c>
+      <c r="C253">
+        <v>10700</v>
+      </c>
+      <c r="D253">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>19</v>
+      </c>
+      <c r="B254">
+        <v>0.103473209758038</v>
+      </c>
+      <c r="C254">
+        <v>9756</v>
+      </c>
+      <c r="D254">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>19.5</v>
+      </c>
+      <c r="B255">
+        <v>0.103544459380177</v>
+      </c>
+      <c r="C255">
+        <v>9224</v>
+      </c>
+      <c r="D255">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>20</v>
+      </c>
+      <c r="B256">
+        <v>0.103692161821389</v>
+      </c>
+      <c r="C256">
+        <v>8408</v>
+      </c>
+      <c r="D256">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>20.5</v>
+      </c>
+      <c r="B257">
+        <v>0.103894330453182</v>
+      </c>
+      <c r="C257">
+        <v>7452</v>
+      </c>
+      <c r="D257">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>21</v>
+      </c>
+      <c r="B258">
+        <v>0.10397632447156</v>
+      </c>
+      <c r="C258">
+        <v>7040</v>
+      </c>
+      <c r="D258">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>21.5</v>
+      </c>
+      <c r="B259">
+        <v>0.104103426589179</v>
+      </c>
+      <c r="C259">
+        <v>5820</v>
+      </c>
+      <c r="D259">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>22</v>
+      </c>
+      <c r="B260">
+        <v>0.104168300941342</v>
+      </c>
+      <c r="C260">
+        <v>4880</v>
+      </c>
+      <c r="D260">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>22.5</v>
+      </c>
+      <c r="B261">
+        <v>0.10423237521474</v>
+      </c>
+      <c r="C261">
+        <v>3936</v>
+      </c>
+      <c r="D261">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>23</v>
+      </c>
+      <c r="B262">
+        <v>0.104043630489948</v>
+      </c>
+      <c r="C262">
+        <v>2999</v>
+      </c>
+      <c r="D262">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>23.5</v>
+      </c>
+      <c r="B263">
+        <v>0.103704309026036</v>
+      </c>
+      <c r="C263">
+        <v>2180</v>
+      </c>
+      <c r="D263">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>24</v>
+      </c>
+      <c r="B264">
+        <v>0.102967354103371</v>
+      </c>
+      <c r="C264">
+        <v>1620</v>
+      </c>
+      <c r="D264">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>24.5</v>
+      </c>
+      <c r="B265">
+        <v>0.101771171519298</v>
+      </c>
+      <c r="C265">
+        <v>1208</v>
+      </c>
+      <c r="D265">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>25</v>
+      </c>
+      <c r="B266">
+        <v>0.100562393285666</v>
+      </c>
+      <c r="C266">
+        <v>942</v>
+      </c>
+      <c r="D266">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>25.5</v>
+      </c>
+      <c r="B267">
+        <v>0.0994973378638699</v>
+      </c>
+      <c r="C267">
+        <v>584</v>
+      </c>
+      <c r="D267">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>26</v>
+      </c>
+      <c r="B268">
+        <v>0.098860136220153</v>
+      </c>
+      <c r="C268">
+        <v>284</v>
+      </c>
+      <c r="D268">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>26.5</v>
+      </c>
+      <c r="B269">
+        <v>0.0986057122548421</v>
+      </c>
+      <c r="C269">
+        <v>192</v>
+      </c>
+      <c r="D269">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>27</v>
+      </c>
+      <c r="B270">
+        <v>0.0982668216411884</v>
+      </c>
+      <c r="C270">
+        <v>104</v>
+      </c>
+      <c r="D270">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>27.5</v>
+      </c>
+      <c r="B271">
+        <v>0.0982306798299154</v>
+      </c>
+      <c r="C271">
+        <v>24</v>
+      </c>
+      <c r="D271">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>28</v>
+      </c>
+      <c r="B272">
+        <v>0.0983734130859375</v>
+      </c>
+      <c r="C272">
+        <v>1</v>
+      </c>
+      <c r="D272">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>0</v>
+      </c>
+      <c r="B274">
+        <v>0.321544647216797</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>0.5</v>
+      </c>
+      <c r="B275">
+        <v>0.251918792724609</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>1</v>
+      </c>
+      <c r="B276">
+        <v>0.206989288330078</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>1.5</v>
+      </c>
+      <c r="B277">
+        <v>0.173709869384766</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>2</v>
+      </c>
+      <c r="B278">
+        <v>0.149250030517578</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>2.5</v>
+      </c>
+      <c r="B279">
+        <v>0.1318359375</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>3</v>
+      </c>
+      <c r="B280">
+        <v>0.120784759521484</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>3.5</v>
+      </c>
+      <c r="B281">
+        <v>0.114452362060547</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>4</v>
+      </c>
+      <c r="B282">
+        <v>0.112628936767578</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>4.5</v>
+      </c>
+      <c r="B283">
+        <v>0.111530303955078</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>5</v>
+      </c>
+      <c r="B284">
+        <v>0.111347198486328</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>5.5</v>
+      </c>
+      <c r="B285">
+        <v>0.11016845703125</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>6</v>
+      </c>
+      <c r="B286">
+        <v>0.108531951904297</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>6.5</v>
+      </c>
+      <c r="B287">
+        <v>0.106643676757812</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>7</v>
+      </c>
+      <c r="B288">
+        <v>0.105297088623047</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>7.5</v>
+      </c>
+      <c r="B289">
+        <v>0.104259490966797</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>8</v>
+      </c>
+      <c r="B290">
+        <v>0.104007720947266</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>8.5</v>
+      </c>
+      <c r="B291">
+        <v>0.104534149169922</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>9</v>
+      </c>
+      <c r="B292">
+        <v>0.104854583740234</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>9.5</v>
+      </c>
+      <c r="B293">
+        <v>0.105121612548828</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>10</v>
+      </c>
+      <c r="B294">
+        <v>0.105052947998047</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>10.5</v>
+      </c>
+      <c r="B295">
+        <v>0.104812622070312</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>11</v>
+      </c>
+      <c r="B296">
+        <v>0.10400390625</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>11.5</v>
+      </c>
+      <c r="B297">
+        <v>0.103054046630859</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>12</v>
+      </c>
+      <c r="B298">
+        <v>0.102573394775391</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>12.5</v>
+      </c>
+      <c r="B299">
+        <v>0.102100372314453</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>13</v>
+      </c>
+      <c r="B300">
+        <v>0.101238250732422</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>13.5</v>
+      </c>
+      <c r="B301">
+        <v>0.10052490234375</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>14</v>
+      </c>
+      <c r="B302">
+        <v>0.100086212158203</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>14.5</v>
+      </c>
+      <c r="B303">
+        <v>0.09991455078125</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>15</v>
+      </c>
+      <c r="B304">
+        <v>0.0994377136230469</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>15.5</v>
+      </c>
+      <c r="B305">
+        <v>0.0985984802246094</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>16</v>
+      </c>
+      <c r="B306">
+        <v>0.0982589721679688</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>0</v>
+      </c>
+      <c r="B308">
+        <v>0.321544647216797</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>0.5</v>
+      </c>
+      <c r="B309">
+        <v>0.252986907958984</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>1</v>
+      </c>
+      <c r="B310">
+        <v>0.208892822265625</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>1.5</v>
+      </c>
+      <c r="B311">
+        <v>0.175731658935547</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>2</v>
+      </c>
+      <c r="B312">
+        <v>0.150863647460938</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>2.5</v>
+      </c>
+      <c r="B313">
+        <v>0.132648468017578</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>3</v>
+      </c>
+      <c r="B314">
+        <v>0.121097564697266</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>3.5</v>
+      </c>
+      <c r="B315">
+        <v>0.11328125</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>4</v>
+      </c>
+      <c r="B316">
+        <v>0.109539031982422</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>4.5</v>
+      </c>
+      <c r="B317">
+        <v>0.106700897216797</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>5</v>
+      </c>
+      <c r="B318">
+        <v>0.10589599609375</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>5.5</v>
+      </c>
+      <c r="B319">
+        <v>0.105075836181641</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>6</v>
+      </c>
+      <c r="B320">
+        <v>0.104820251464844</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>6.5</v>
+      </c>
+      <c r="B321">
+        <v>0.104709625244141</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>7</v>
+      </c>
+      <c r="B322">
+        <v>0.104629516601562</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>7.5</v>
+      </c>
+      <c r="B323">
+        <v>0.104354858398438</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>8</v>
+      </c>
+      <c r="B324">
+        <v>0.104076385498047</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>8.5</v>
+      </c>
+      <c r="B325">
+        <v>0.103546142578125</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>9</v>
+      </c>
+      <c r="B326">
+        <v>0.10284423828125</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327">
+        <v>9.5</v>
+      </c>
+      <c r="B327">
+        <v>0.101482391357422</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>10</v>
+      </c>
+      <c r="B328">
+        <v>0.0998268127441406</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>10.5</v>
+      </c>
+      <c r="B329">
+        <v>0.0980339050292969</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>11</v>
+      </c>
+      <c r="B330">
+        <v>0.0968093872070312</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>11.5</v>
+      </c>
+      <c r="B331">
+        <v>0.0958175659179688</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>12</v>
+      </c>
+      <c r="B332">
+        <v>0.0956993103027344</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>12.5</v>
+      </c>
+      <c r="B333">
+        <v>0.0959663391113281</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>13</v>
+      </c>
+      <c r="B334">
+        <v>0.0960578918457031</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>13.5</v>
+      </c>
+      <c r="B335">
+        <v>0.0965690612792969</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>14</v>
+      </c>
+      <c r="B336">
+        <v>0.0970230102539062</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>14.5</v>
+      </c>
+      <c r="B337">
+        <v>0.0978813171386719</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>15</v>
+      </c>
+      <c r="B338">
+        <v>0.0984039306640625</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>15.5</v>
+      </c>
+      <c r="B339">
+        <v>0.0984344482421875</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>16</v>
+      </c>
+      <c r="B340">
+        <v>0.0987548828125</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>0</v>
+      </c>
+      <c r="B342">
+        <v>0.321544647216797</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>0.5</v>
+      </c>
+      <c r="B343">
+        <v>0.2513427734375</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>1</v>
+      </c>
+      <c r="B344">
+        <v>0.206008911132812</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>1.5</v>
+      </c>
+      <c r="B345">
+        <v>0.172321319580078</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>2</v>
+      </c>
+      <c r="B346">
+        <v>0.146327972412109</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>2.5</v>
+      </c>
+      <c r="B347">
+        <v>0.128185272216797</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>3</v>
+      </c>
+      <c r="B348">
+        <v>0.115978240966797</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>3.5</v>
+      </c>
+      <c r="B349">
+        <v>0.108123779296875</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>4</v>
+      </c>
+      <c r="B350">
+        <v>0.104946136474609</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>4.5</v>
+      </c>
+      <c r="B351">
+        <v>0.103485107421875</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>5</v>
+      </c>
+      <c r="B352">
+        <v>0.103527069091797</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>5.5</v>
+      </c>
+      <c r="B353">
+        <v>0.102748870849609</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>6</v>
+      </c>
+      <c r="B354">
+        <v>0.102329254150391</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>6.5</v>
+      </c>
+      <c r="B355">
+        <v>0.101631164550781</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>7</v>
+      </c>
+      <c r="B356">
+        <v>0.100929260253906</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>7.5</v>
+      </c>
+      <c r="B357">
+        <v>0.100593566894531</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>8</v>
+      </c>
+      <c r="B358">
+        <v>0.100269317626953</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>8.5</v>
+      </c>
+      <c r="B359">
+        <v>0.100086212158203</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>9</v>
+      </c>
+      <c r="B360">
+        <v>0.100578308105469</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361">
+        <v>9.5</v>
+      </c>
+      <c r="B361">
+        <v>0.101413726806641</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>10</v>
+      </c>
+      <c r="B362">
+        <v>0.101974487304688</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>10.5</v>
+      </c>
+      <c r="B363">
+        <v>0.102272033691406</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>11</v>
+      </c>
+      <c r="B364">
+        <v>0.102855682373047</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>11.5</v>
+      </c>
+      <c r="B365">
+        <v>0.103504180908203</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>12</v>
+      </c>
+      <c r="B366">
+        <v>0.103351593017578</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>12.5</v>
+      </c>
+      <c r="B367">
+        <v>0.102878570556641</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>13</v>
+      </c>
+      <c r="B368">
+        <v>0.101905822753906</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>13.5</v>
+      </c>
+      <c r="B369">
+        <v>0.100757598876953</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>14</v>
+      </c>
+      <c r="B370">
+        <v>0.099700927734375</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>14.5</v>
+      </c>
+      <c r="B371">
+        <v>0.0990371704101562</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>15</v>
+      </c>
+      <c r="B372">
+        <v>0.0979766845703125</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>15.5</v>
+      </c>
+      <c r="B373">
+        <v>0.0967788696289062</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>16</v>
+      </c>
+      <c r="B374">
+        <v>0.0962905883789062</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>